--- a/output/quickfixclose4_portfolio_daily.xlsx
+++ b/output/quickfixclose4_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>262,563.48</t>
+          <t>306,497.96</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+162.56%</t>
+          <t>+206.50%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>271,776  (+171.78%)</t>
+          <t>317,506  (+217.51%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,723  (9.2 pts of return)</t>
+          <t>5,022  (11.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11.8x</t>
+          <t>15.0x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.6 bars</t>
+          <t>2.7 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+5.12R  (best +24.42R)</t>
+          <t>+5.55R  (best +24.42R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,026  (+5.12%)</t>
+          <t>8,152  (+5.55%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,587  (-1.32%)</t>
+          <t>-1,609  (-1.31%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>71% of trading days</t>
+          <t>72% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5671,22 +5671,74 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>262563.48</v>
+        <v>262682.37</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>0</v>
+        <v>4540.93</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>262563.48</v>
+        <v>258141.44</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>309118.46</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>2259.05</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>306859.41</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures exit_close (+46,436)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>306497.96</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>306497.96</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures stop (-2,621)</t>
         </is>
       </c>
     </row>
@@ -9985,14 +10037,22 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4</v>
+      </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>20.375</v>
       </c>
       <c r="G84" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.013</v>
+        <v>20.35</v>
       </c>
       <c r="I84" s="5" t="n">
         <v>296240.73</v>
@@ -10000,15 +10060,15 @@
       <c r="J84" s="5" t="n">
         <v>4117.75</v>
       </c>
-      <c r="K84" s="6" t="n">
-        <v>-51.47</v>
+      <c r="K84" s="7" t="n">
+        <v>83796.13</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>358671.31</v>
+        <v>442681.33</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10028,14 +10088,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4</v>
+      </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>292122.98</v>
@@ -10044,14 +10112,14 @@
         <v>4060.51</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>-162.42</v>
+        <v>-4710.19</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>358722.78</v>
+        <v>437971.14</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose4_portfolio_daily.xlsx
+++ b/output/quickfixclose4_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>306,497.96</t>
+          <t>306,481.43</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+206.50%</t>
+          <t>+206.48%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,022  (11.0 pts of return)</t>
+          <t>5,039  (11.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>72% of trading days</t>
+          <t>71% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5742,6 +5742,62 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>306497.96</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>9103.299999999999</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>297394.67</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 3,065); Nasdaq_100_E_mini short (risk 3,034); S_P_500_E_mini short (risk 3,004)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>306481.43</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>306481.43</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,974)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5754,7 +5810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10123,6 +10179,178 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>437971.14</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>6087.8</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-21.14</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>437939.7</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>431883.34</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>6003.18</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>437960.83</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>425880.17</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>5919.73</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>437938.44</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>419960.43</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>5837.45</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>437961.16</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixclose4_portfolio_daily.xlsx
+++ b/output/quickfixclose4_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>306,481.43</t>
+          <t>303,472.85</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+206.48%</t>
+          <t>+203.47%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>317,506  (+217.51%)</t>
+          <t>314,426  (+214.43%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,039  (11.0 pts of return)</t>
+          <t>5,073  (11.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15.0x</t>
+          <t>14.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.7 bars</t>
+          <t>2.6 bars</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,609  (-1.31%)</t>
+          <t>-1,636  (-1.31%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>71% of trading days</t>
+          <t>72% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5775,26 +5775,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>306481.43</v>
+        <v>306497.96</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>0</v>
+        <v>12077.24</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>306481.43</v>
+        <v>294420.72</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>Gold_Futures_COMEX short (risk 2,974)</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>303472.85</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>303472.85</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,944); NY_Palladium_Futures short (risk 2,915)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-2,994); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10214,7 +10242,7 @@
         <v>-21.14</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>437939.7</v>
+        <v>432034.49</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -10257,7 +10285,7 @@
         <v>-0.33</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>437960.83</v>
+        <v>432093.45</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -10300,7 +10328,7 @@
         <v>-1.25</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>437938.44</v>
+        <v>432033.24</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -10324,14 +10352,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>419960.43</v>
@@ -10340,12 +10376,98 @@
         <v>5837.45</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>-9.98</v>
+        <v>-5877.36</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>437961.16</v>
+        <v>432093.78</v>
       </c>
       <c r="M89" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>414122.98</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>5756.31</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>-15.56</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>432077.89</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>408366.67</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>5676.3</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>-22.26</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>432055.63</v>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
